--- a/artfynd/A 40113-2023 artfynd.xlsx
+++ b/artfynd/A 40113-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40113-2023 artfynd.xlsx
+++ b/artfynd/A 40113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76303205</v>
+        <v>112818813</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräntberget, Högland, Ång</t>
+          <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704101.9584387769</v>
+        <v>704162</v>
       </c>
       <c r="R2" t="n">
-        <v>7070018.947746278</v>
+        <v>7069914</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,53 +764,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112818812</v>
+        <v>112818790</v>
       </c>
       <c r="B3" t="n">
-        <v>90378</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704027</v>
+        <v>704032</v>
       </c>
       <c r="R3" t="n">
-        <v>7070206</v>
+        <v>7070257</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112818880</v>
+        <v>112818791</v>
       </c>
       <c r="B4" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704096</v>
+        <v>704019</v>
       </c>
       <c r="R4" t="n">
-        <v>7070017</v>
+        <v>7070204</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112818873</v>
+        <v>112818793</v>
       </c>
       <c r="B5" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>704073</v>
+        <v>704034</v>
       </c>
       <c r="R5" t="n">
-        <v>7070053</v>
+        <v>7070135</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112818813</v>
+        <v>112818794</v>
       </c>
       <c r="B6" t="n">
-        <v>90219</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>704162</v>
+        <v>704058</v>
       </c>
       <c r="R6" t="n">
-        <v>7069913</v>
+        <v>7070084</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112818872</v>
+        <v>112818795</v>
       </c>
       <c r="B7" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704058</v>
+        <v>704134</v>
       </c>
       <c r="R7" t="n">
-        <v>7070084</v>
+        <v>7069925</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112818768</v>
+        <v>112818812</v>
       </c>
       <c r="B8" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704144</v>
+        <v>704027</v>
       </c>
       <c r="R8" t="n">
-        <v>7069782</v>
+        <v>7070206</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112818777</v>
+        <v>112818766</v>
       </c>
       <c r="B9" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704012</v>
+        <v>704151</v>
       </c>
       <c r="R9" t="n">
-        <v>7070190</v>
+        <v>7069881</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112818879</v>
+        <v>112818767</v>
       </c>
       <c r="B10" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>704099</v>
+        <v>704188</v>
       </c>
       <c r="R10" t="n">
-        <v>7070026</v>
+        <v>7069819</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112818868</v>
+        <v>112818768</v>
       </c>
       <c r="B11" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>704067</v>
+        <v>704144</v>
       </c>
       <c r="R11" t="n">
-        <v>7070211</v>
+        <v>7069781</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112818802</v>
+        <v>112818773</v>
       </c>
       <c r="B12" t="n">
-        <v>55972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1783,21 +1718,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>704074</v>
+        <v>704023</v>
       </c>
       <c r="R12" t="n">
-        <v>7069998</v>
+        <v>7070262</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112818836</v>
+        <v>112818774</v>
       </c>
       <c r="B13" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1900,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>704102</v>
+        <v>704052</v>
       </c>
       <c r="R13" t="n">
-        <v>7070049</v>
+        <v>7070260</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1962,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112818830</v>
+        <v>112818775</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2006,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>704076</v>
+        <v>704105</v>
       </c>
       <c r="R14" t="n">
-        <v>7070016</v>
+        <v>7070258</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2068,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112818778</v>
+        <v>112818776</v>
       </c>
       <c r="B15" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>704039</v>
+        <v>704031</v>
       </c>
       <c r="R15" t="n">
-        <v>7070178</v>
+        <v>7070248</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2174,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112818870</v>
+        <v>112818777</v>
       </c>
       <c r="B16" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2218,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>704040</v>
+        <v>704012</v>
       </c>
       <c r="R16" t="n">
-        <v>7070143</v>
+        <v>7070190</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2280,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112818878</v>
+        <v>112818778</v>
       </c>
       <c r="B17" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2324,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>704117</v>
+        <v>704039</v>
       </c>
       <c r="R17" t="n">
-        <v>7070037</v>
+        <v>7070178</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112818874</v>
+        <v>112818779</v>
       </c>
       <c r="B18" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2430,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>704051</v>
+        <v>704026</v>
       </c>
       <c r="R18" t="n">
-        <v>7070055</v>
+        <v>7070141</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,37 +2392,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112818882</v>
+        <v>112818780</v>
       </c>
       <c r="B19" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2536,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>704132</v>
+        <v>704070</v>
       </c>
       <c r="R19" t="n">
-        <v>7069982</v>
+        <v>7070051</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2598,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112818776</v>
+        <v>112818781</v>
       </c>
       <c r="B20" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,10 +2532,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>704031</v>
+        <v>704061</v>
       </c>
       <c r="R20" t="n">
-        <v>7070248</v>
+        <v>7070050</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2704,37 +2594,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112818867</v>
+        <v>112818782</v>
       </c>
       <c r="B21" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2748,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>704086</v>
+        <v>704066</v>
       </c>
       <c r="R21" t="n">
-        <v>7070211</v>
+        <v>7070058</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2810,19 +2695,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112818875</v>
+        <v>112818843</v>
       </c>
       <c r="B22" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2854,10 +2734,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>704077</v>
+        <v>704146</v>
       </c>
       <c r="R22" t="n">
-        <v>7070044</v>
+        <v>7069763</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2916,19 +2796,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112818869</v>
+        <v>112818865</v>
       </c>
       <c r="B23" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2960,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>704040</v>
+        <v>704087</v>
       </c>
       <c r="R23" t="n">
-        <v>7070166</v>
+        <v>7070293</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3022,32 +2897,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112818833</v>
+        <v>112818866</v>
       </c>
       <c r="B24" t="n">
-        <v>90323</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3055,19 +2930,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>704033</v>
+        <v>704094</v>
       </c>
       <c r="R24" t="n">
-        <v>7070147</v>
+        <v>7070242</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3108,7 +2980,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3127,37 +2998,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112818775</v>
+        <v>112818867</v>
       </c>
       <c r="B25" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3171,10 +3037,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>704105</v>
+        <v>704086</v>
       </c>
       <c r="R25" t="n">
-        <v>7070258</v>
+        <v>7070211</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3233,37 +3099,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112818766</v>
+        <v>112818868</v>
       </c>
       <c r="B26" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3277,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>704151</v>
+        <v>704067</v>
       </c>
       <c r="R26" t="n">
-        <v>7069882</v>
+        <v>7070210</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3339,37 +3200,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112818791</v>
+        <v>112818869</v>
       </c>
       <c r="B27" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3383,10 +3239,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>704019</v>
+        <v>704040</v>
       </c>
       <c r="R27" t="n">
-        <v>7070204</v>
+        <v>7070166</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3445,37 +3301,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112818790</v>
+        <v>112818870</v>
       </c>
       <c r="B28" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3489,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>704032</v>
+        <v>704040</v>
       </c>
       <c r="R28" t="n">
-        <v>7070257</v>
+        <v>7070143</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3551,32 +3402,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112818887</v>
+        <v>112818871</v>
       </c>
       <c r="B29" t="n">
-        <v>79114</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3595,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>704082</v>
+        <v>704033</v>
       </c>
       <c r="R29" t="n">
-        <v>7070019</v>
+        <v>7070101</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3657,19 +3503,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112818871</v>
+        <v>112818872</v>
       </c>
       <c r="B30" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3701,10 +3542,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>704033</v>
+        <v>704058</v>
       </c>
       <c r="R30" t="n">
-        <v>7070101</v>
+        <v>7070084</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3763,37 +3604,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112818767</v>
+        <v>112818873</v>
       </c>
       <c r="B31" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3807,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>704187</v>
+        <v>704072</v>
       </c>
       <c r="R31" t="n">
-        <v>7069819</v>
+        <v>7070052</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3869,37 +3705,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112818838</v>
+        <v>112818874</v>
       </c>
       <c r="B32" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3913,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>704162</v>
+        <v>704050</v>
       </c>
       <c r="R32" t="n">
-        <v>7069874</v>
+        <v>7070055</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3975,37 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112818794</v>
+        <v>112818875</v>
       </c>
       <c r="B33" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4019,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>704058</v>
+        <v>704077</v>
       </c>
       <c r="R33" t="n">
-        <v>7070084</v>
+        <v>7070045</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4081,19 +3907,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112818866</v>
+        <v>112818876</v>
       </c>
       <c r="B34" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4125,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>704094</v>
+        <v>704135</v>
       </c>
       <c r="R34" t="n">
-        <v>7070242</v>
+        <v>7070061</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4187,19 +4008,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112818884</v>
+        <v>112818878</v>
       </c>
       <c r="B35" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4231,10 +4047,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>704136</v>
+        <v>704117</v>
       </c>
       <c r="R35" t="n">
-        <v>7069914</v>
+        <v>7070037</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4293,19 +4109,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112818865</v>
+        <v>112818879</v>
       </c>
       <c r="B36" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4337,10 +4148,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>704086</v>
+        <v>704099</v>
       </c>
       <c r="R36" t="n">
-        <v>7070294</v>
+        <v>7070026</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4399,37 +4210,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112818808</v>
+        <v>112818880</v>
       </c>
       <c r="B37" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4437,21 +4243,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>704032</v>
+        <v>704096</v>
       </c>
       <c r="R37" t="n">
-        <v>7070257</v>
+        <v>7070017</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4510,37 +4311,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112818782</v>
+        <v>112818881</v>
       </c>
       <c r="B38" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4554,10 +4350,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>704066</v>
+        <v>704137</v>
       </c>
       <c r="R38" t="n">
-        <v>7070058</v>
+        <v>7069994</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4616,37 +4412,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112818795</v>
+        <v>112818882</v>
       </c>
       <c r="B39" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4660,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>704134</v>
+        <v>704131</v>
       </c>
       <c r="R39" t="n">
-        <v>7069925</v>
+        <v>7069982</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4722,37 +4513,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112818774</v>
+        <v>112818883</v>
       </c>
       <c r="B40" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4766,10 +4552,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>704052</v>
+        <v>704134</v>
       </c>
       <c r="R40" t="n">
-        <v>7070260</v>
+        <v>7069974</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4828,37 +4614,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112818793</v>
+        <v>112818884</v>
       </c>
       <c r="B41" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4872,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>704033</v>
+        <v>704136</v>
       </c>
       <c r="R41" t="n">
-        <v>7070135</v>
+        <v>7069914</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4934,15 +4715,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112818843</v>
+        <v>112818830</v>
       </c>
       <c r="B42" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4950,21 +4726,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4978,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>704146</v>
+        <v>704076</v>
       </c>
       <c r="R42" t="n">
-        <v>7069763</v>
+        <v>7070017</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5040,32 +4816,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112818876</v>
+        <v>112818887</v>
       </c>
       <c r="B43" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5084,10 +4855,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>704134</v>
+        <v>704082</v>
       </c>
       <c r="R43" t="n">
-        <v>7070062</v>
+        <v>7070019</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5146,37 +4917,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112818881</v>
+        <v>112818808</v>
       </c>
       <c r="B44" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5184,16 +4950,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>704137</v>
+        <v>704032</v>
       </c>
       <c r="R44" t="n">
-        <v>7069995</v>
+        <v>7070257</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5252,37 +5023,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112818883</v>
+        <v>112818801</v>
       </c>
       <c r="B45" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5290,16 +5056,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>704134</v>
+        <v>704054</v>
       </c>
       <c r="R45" t="n">
-        <v>7069974</v>
+        <v>7069950</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5358,15 +5129,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112818801</v>
+        <v>112818802</v>
       </c>
       <c r="B46" t="n">
-        <v>55972</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5407,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>704054</v>
+        <v>704075</v>
       </c>
       <c r="R46" t="n">
-        <v>7069950</v>
+        <v>7069998</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5469,37 +5235,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112818779</v>
+        <v>112818836</v>
       </c>
       <c r="B47" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5513,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>704026</v>
+        <v>704102</v>
       </c>
       <c r="R47" t="n">
-        <v>7070141</v>
+        <v>7070049</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5575,15 +5336,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112818841</v>
+        <v>112818833</v>
       </c>
       <c r="B48" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5591,21 +5347,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6040186</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5613,16 +5369,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nördberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>704016</v>
+        <v>704032</v>
       </c>
       <c r="R48" t="n">
-        <v>7070185</v>
+        <v>7070147</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5663,6 +5422,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5678,430 +5438,6 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>112818773</v>
-      </c>
-      <c r="B49" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Nördberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>704023</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7070262</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>112818780</v>
-      </c>
-      <c r="B50" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Nördberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>704070</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7070052</v>
-      </c>
-      <c r="S50" t="n">
-        <v>5</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>112818781</v>
-      </c>
-      <c r="B51" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Nördberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>704062</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7070051</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>112818842</v>
-      </c>
-      <c r="B52" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Nördberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>704069</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7070092</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40113-2023 artfynd.xlsx
+++ b/artfynd/A 40113-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818813</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818790</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818793</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818794</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818795</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818812</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818767</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818773</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818774</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818775</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818776</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818777</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818778</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818779</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818780</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818781</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818782</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818843</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818865</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818866</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818867</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818868</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818869</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818870</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818871</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818872</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818873</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3803,6 +3958,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818874</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3904,6 +4064,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818875</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4005,6 +4170,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818876</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4106,6 +4276,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818878</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4207,6 +4382,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818879</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4308,6 +4488,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818880</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4409,6 +4594,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818881</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4510,6 +4700,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818882</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4611,6 +4806,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818883</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4712,6 +4912,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818884</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4813,6 +5018,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818830</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4914,6 +5124,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818887</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5020,6 +5235,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818808</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5126,6 +5346,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818801</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5232,6 +5457,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818802</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5333,6 +5563,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818836</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5438,8 +5673,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>